--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
   <si>
     <t xml:space="preserve">VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -242,16 +242,13 @@
     <t xml:space="preserve">Loop (lc)</t>
   </si>
   <si>
-    <t xml:space="preserve">F02_Cond01 &gt; 100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F02_Cond02 &lt; 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F02_Cond03 == i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F02_Condnn &lt; n</t>
+    <t xml:space="preserve">item.getQuantity() &gt; 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F02_Conp.getCategorie() == SMOOTHIEd02 &lt; 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total &gt; 100.0</t>
   </si>
   <si>
     <t xml:space="preserve">F02_P01</t>
@@ -260,27 +257,45 @@
     <t xml:space="preserve">F02_P02</t>
   </si>
   <si>
-    <t xml:space="preserve">F02_Pnn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m&lt;n</t>
-  </si>
-  <si>
     <t xml:space="preserve">T</t>
   </si>
   <si>
     <t xml:space="preserve">F</t>
   </si>
   <si>
+    <t xml:space="preserve">TC01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tea, Qty: 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoothie, Qty: 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juice, Qty: 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tea(2) + Smoothie(1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">WBT Implemented TCs</t>
   </si>
   <si>
@@ -290,37 +305,49 @@
     <t xml:space="preserve">Req. ID</t>
   </si>
   <si>
-    <t xml:space="preserve">TC No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">actual result</t>
+    <t xml:space="preserve">input: Produse (ID)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input: Cantitate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input: Categorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output: expected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output: actual result</t>
   </si>
   <si>
     <t xml:space="preserve">F02</t>
   </si>
   <si>
-    <t xml:space="preserve">F02_TC01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F02_TC02</t>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMOOTHIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104, 105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEA, SMOOTHIE</t>
   </si>
   <si>
     <t xml:space="preserve">Statistics</t>
   </si>
   <si>
     <t xml:space="preserve">Testare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depanare</t>
   </si>
   <si>
     <t xml:space="preserve">Re-testare</t>
@@ -353,80 +380,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">passed</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">#TCs </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">falied</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Coverage (%)</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[se va prelua valoarea indicata in raportul de acoperire pentru metoda testata]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">#Bugs </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[se va indica numarul de bug-uri identificate prin depanare, la nivelul metodei testate]</t>
     </r>
   </si>
   <si>
@@ -500,31 +453,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">failed</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Coverage (%) </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[se va prelua valoarea indicata in raportul de acoperire pentru metoda testata]</t>
     </r>
   </si>
   <si>
@@ -699,15 +627,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -760,7 +688,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -823,18 +751,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99FFCC"/>
-        <bgColor rgb="FFC6D9F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF99"/>
         <bgColor rgb="FFFDEADA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -878,44 +800,9 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="double"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="double"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="double"/>
       <top/>
-      <bottom style="double"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
       <bottom style="double"/>
       <diagonal/>
     </border>
@@ -957,13 +844,6 @@
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
-      <top style="double"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="double"/>
       <top/>
       <bottom style="thin"/>
       <diagonal/>
@@ -979,13 +859,6 @@
       <left style="thin"/>
       <right/>
       <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="double"/>
-      <top style="double"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -1036,292 +909,248 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="11" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="23" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="12" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="12" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="23" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="12" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="24" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1369,12 +1198,12 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FF99FFCC"/>
+      <rgbColor rgb="FFFDEADA"/>
       <rgbColor rgb="FFD7E4BD"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF8EB4E3"/>
       <rgbColor rgb="FFF2DCDB"/>
-      <rgbColor rgb="FFFDEADA"/>
+      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFE6B9B8"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -1408,9 +1237,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>422640</xdr:colOff>
+      <xdr:colOff>421920</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1161360</xdr:rowOff>
+      <xdr:rowOff>1160640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1424,7 +1253,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="567720" y="1218240"/>
-          <a:ext cx="4907160" cy="2344680"/>
+          <a:ext cx="4906440" cy="2343960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1438,31 +1267,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>621000</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>125640</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>194040</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>4320</xdr:rowOff>
-    </xdr:to>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>469440</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>562680</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>240120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>344520</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>87120</xdr:rowOff>
+      <xdr:colOff>343800</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>180720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1476,7 +1290,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3395520" y="10077480"/>
-          <a:ext cx="6961680" cy="6981120"/>
+          <a:ext cx="6960960" cy="6980400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1675,116 +1489,116 @@
   <dimension ref="B1:P20"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="19.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="19.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7" t="s">
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="N7" s="7" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="N7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="N8" s="7" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="N8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="N9" s="7" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="N9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4"/>
+      <c r="B19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4"/>
+      <c r="B20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1809,384 +1623,384 @@
   <dimension ref="B1:T27"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="10.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="I6" s="11" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="I6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="Q6" s="11" t="s">
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="Q6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="87.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="I8" s="1" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="I8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="Q8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="15" t="s">
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="145.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="Q9" s="14" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="Q9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="15" t="s">
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="145.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="I10" s="18" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="I10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="Q10" s="14" t="s">
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="Q10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="R10" s="14" t="s">
+      <c r="R10" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="S10" s="14"/>
-      <c r="T10" s="15" t="s">
+      <c r="S10" s="15"/>
+      <c r="T10" s="16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="Q13" s="11" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="Q13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="Q15" s="12" t="s">
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="Q15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R15" s="12" t="s">
+      <c r="R15" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="16.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="Q16" s="15" t="s">
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="Q16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="74.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="Q17" s="15" t="s">
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="73.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="Q17" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="60.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="Q18" s="15" t="s">
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="Q18" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="Q19" s="15" t="s">
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="Q19" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="73.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="Q20" s="15" t="s">
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="Q20" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="Q21" s="15" t="s">
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="Q21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="R21" s="19" t="s">
+      <c r="R21" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="60.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="Q22" s="15" t="s">
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="Q22" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="R22" s="19" t="s">
+      <c r="R22" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="Q23" s="15" t="s">
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="Q23" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="R23" s="19" t="s">
+      <c r="R23" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-      <c r="Q24" s="15" t="s">
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="Q24" s="16" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q25" s="15" t="s">
+      <c r="Q25" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q26" s="15" t="s">
+      <c r="Q26" s="16" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q27" s="15" t="s">
+      <c r="Q27" s="16" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2236,451 +2050,348 @@
     <tabColor rgb="FFCCC1DA"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:AB16"/>
+  <dimension ref="B1:N16"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="0" width="2.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="2.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="4.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="5.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="2.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16371" style="0" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20"/>
+      <c r="B5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="17.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="21"/>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="17.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="24" t="s">
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="25" t="s">
+      <c r="M7" s="25"/>
+      <c r="N7" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="W7" s="25"/>
-      <c r="X7" s="25"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="25"/>
-      <c r="AA7" s="25"/>
-      <c r="AB7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21"/>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23" t="s">
+      <c r="E8" s="23"/>
+      <c r="F8" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23" t="s">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23" t="s">
+      <c r="I8" s="28"/>
+      <c r="J8" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23" t="s">
+      <c r="K8" s="28"/>
+      <c r="L8" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="O8" s="23"/>
-      <c r="P8" s="24" t="s">
+      <c r="M8" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="Q8" s="24" t="s">
+      <c r="N8" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="22"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="R8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="S8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="T8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="U8" s="24" t="s">
+      <c r="G9" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="V8" s="25" t="n">
+      <c r="H9" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="26"/>
+    </row>
+    <row r="10" customFormat="false" ht="17.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z8" s="25" t="s">
+      <c r="E10" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="32"/>
+      <c r="N10" s="33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="31"/>
+      <c r="I11" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="31"/>
+      <c r="K11" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>47</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="31"/>
+      <c r="L13" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="M13" s="32"/>
+      <c r="N13" s="33"/>
+    </row>
+    <row r="14" customFormat="false" ht="17.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="30" t="n">
         <v>67</v>
       </c>
-      <c r="AA8" s="25" t="s">
+      <c r="E14" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="AB8" s="25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="21"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="N9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="O9" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="32"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="32"/>
-      <c r="AB10" s="32"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="32"/>
-      <c r="X11" s="32"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="32"/>
-      <c r="AB11" s="32"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="32"/>
-      <c r="W12" s="32"/>
-      <c r="X12" s="32"/>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="32"/>
-      <c r="AA12" s="32"/>
-      <c r="AB12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="32"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="32"/>
-      <c r="AB13" s="32"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="32"/>
-      <c r="Y14" s="32"/>
-      <c r="Z14" s="32"/>
-      <c r="AA14" s="32"/>
-      <c r="AB14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-      <c r="AA15" s="32"/>
-      <c r="AB15" s="32"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="35"/>
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="33"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="17">
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:AB6"/>
+    <mergeCell ref="E6:N6"/>
     <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:U7"/>
-    <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="L7:M7"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2698,421 +2409,286 @@
     <tabColor rgb="FF8EB4E3"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:N16"/>
+  <dimension ref="B1:J15"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+    </row>
+    <row r="5" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="35"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="40"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="37"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="L5" s="41" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="40" t="n">
+      <c r="F6" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="40" t="n">
+      <c r="C7" s="39"/>
+      <c r="D7" s="30" t="n">
+        <v>101</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="37" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="39"/>
+      <c r="D8" s="30" t="n">
+        <v>102</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>47</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="30" t="n">
+        <v>103</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>98</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="39"/>
+      <c r="D10" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>67</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="42"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="46"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="54" t="n">
+        <f aca="false">SUM(C15:C15)</f>
         <v>5</v>
       </c>
-      <c r="F7" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="40" t="n">
-        <v>11</v>
-      </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="41" t="n">
-        <v>13</v>
-      </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="48"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="N13" s="52"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="56" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="J14" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="L14" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="M14" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="N14" s="62" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="53"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="n">
-        <f aca="false">SUM(C16:D16)</f>
+      <c r="C15" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="54" t="n">
+        <f aca="false">SUM(G15:H15)</f>
+        <v>5</v>
+      </c>
+      <c r="G15" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="64"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="67" t="s">
-        <v>99</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <f aca="false">SUM(J16:K16)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="69"/>
-      <c r="M16" s="70" t="s">
-        <v>99</v>
-      </c>
-      <c r="N16" s="71" t="n">
-        <f aca="false">C16</f>
-        <v>0</v>
+      <c r="I15" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="60" t="n">
+        <f aca="false">C15</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:L3"/>
+  <mergeCells count="16">
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="C6:C10"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
